--- a/CoworkPlaybook/samples_air/OneDrive_種入用/AIR1_航班異常/AIR1_受影響旅客清單.xlsx
+++ b/CoworkPlaybook/samples_air/OneDrive_種入用/AIR1_航班異常/AIR1_受影響旅客清單.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -464,6 +464,7 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,6 +518,11 @@
           <t>聯絡方式</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>電子郵件</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -569,6 +575,11 @@
           <t>0912-XXX-101</t>
         </is>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -621,6 +632,11 @@
           <t>監護人 0933-XXX-202</t>
         </is>
       </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -673,6 +689,11 @@
           <t>0928-XXX-303</t>
         </is>
       </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -725,6 +746,11 @@
           <t>0955-XXX-404</t>
         </is>
       </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -777,6 +803,11 @@
           <t>0911-XXX-505</t>
         </is>
       </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -829,6 +860,11 @@
           <t>0966-XXX-606</t>
         </is>
       </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -881,6 +917,11 @@
           <t>0977-XXX-707</t>
         </is>
       </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -931,6 +972,11 @@
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>0988-XXX-808</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>andy@M365CPI90050711.onmicrosoft.com</t>
         </is>
       </c>
     </row>
